--- a/Documentos/Documentos Excel - Hojas de calculo/Funciones de texto.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Funciones de texto.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\herna\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\La pagina web de Hernan\Documentos\Documentos Excel - Hojas de calculo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="110">
   <si>
     <t>Dato</t>
   </si>
@@ -214,33 +214,6 @@
     <t>Encontrar descuento</t>
   </si>
   <si>
-    <t>Juan + 102</t>
-  </si>
-  <si>
-    <t>Unir nombre y código con guion</t>
-  </si>
-  <si>
-    <t>Ana + 205</t>
-  </si>
-  <si>
-    <t>Unir nombre y código</t>
-  </si>
-  <si>
-    <t>Pedro + 330</t>
-  </si>
-  <si>
-    <t>Luis + 441</t>
-  </si>
-  <si>
-    <t>Unir datos en un solo texto</t>
-  </si>
-  <si>
-    <t>Sofia + 512</t>
-  </si>
-  <si>
-    <t>Generar identificador</t>
-  </si>
-  <si>
     <t>juan perez</t>
   </si>
   <si>
@@ -271,9 +244,6 @@
     <t>Convertir a formato empresa</t>
   </si>
   <si>
-    <t>JUAN.PEREZ@MAIL.COM</t>
-  </si>
-  <si>
     <t>Convertir email a minúsculas</t>
   </si>
   <si>
@@ -346,7 +316,49 @@
     <t>Contar caracteres la patente</t>
   </si>
   <si>
-    <t>Crear ID completo (como un videojuego)</t>
+    <t>Unir nombre y apellido</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan </t>
+  </si>
+  <si>
+    <t>Lopez</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Muñoz</t>
+  </si>
+  <si>
+    <t>Cardona</t>
+  </si>
+  <si>
+    <t>Blanco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana </t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofia </t>
+  </si>
+  <si>
+    <t>Unir apellido y nombre</t>
+  </si>
+  <si>
+    <t>JUAN.PEREZ@GMAIL.COM</t>
   </si>
 </sst>
 </file>
@@ -410,7 +422,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -419,6 +431,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Buena" xfId="1" builtinId="26"/>
@@ -1591,15 +1604,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>66674</xdr:rowOff>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2019300</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1608,7 +1621,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="123825" y="1400174"/>
+          <a:off x="152400" y="1285874"/>
           <a:ext cx="3562350" cy="1162051"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2434,46 +2447,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C6" s="2"/>
     </row>
@@ -2506,46 +2519,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2"/>
     </row>
@@ -2743,7 +2756,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
     </row>
@@ -2917,69 +2930,88 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3010,46 +3042,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2"/>
     </row>
@@ -3081,52 +3113,55 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>80</v>
+      <c r="A2" t="s">
+        <v>109</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C6" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>